--- a/CE国試data/CE_questions_2018.xlsx
+++ b/CE国試data/CE_questions_2018.xlsx
@@ -1772,7 +1772,7 @@
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
@@ -2959,7 +2959,7 @@
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="T26" t="inlineStr">
@@ -3848,7 +3848,7 @@
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="T35" t="inlineStr">
@@ -6045,7 +6045,7 @@
       </c>
       <c r="S57" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="T57" t="inlineStr">
@@ -6243,7 +6243,7 @@
       </c>
       <c r="S59" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="T59" t="inlineStr">
@@ -8294,7 +8294,7 @@
       </c>
       <c r="S80" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="T80" t="inlineStr">
@@ -8880,7 +8880,7 @@
       </c>
       <c r="S86" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="T86" t="inlineStr">
@@ -10462,7 +10462,7 @@
       </c>
       <c r="S102" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="T102" t="inlineStr">
@@ -11144,7 +11144,7 @@
       </c>
       <c r="S109" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="T109" t="inlineStr">
@@ -12821,7 +12821,7 @@
       </c>
       <c r="S126" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="T126" t="inlineStr">
@@ -17201,7 +17201,7 @@
       </c>
       <c r="S170" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="T170" t="inlineStr">
